--- a/documentos/transversales/05_Presupuesto_SIGEVET.xlsx
+++ b/documentos/transversales/05_Presupuesto_SIGEVET.xlsx
@@ -887,7 +887,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Oracle AI Database 26ai Free</t>
+          <t>MySQL 8.4 Community</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -955,7 +955,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Python/Flask</t>
+          <t>Java/Tomcat</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Oracle SQL Developer Data Modeler</t>
+          <t>MySQL Workbench Community</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">

--- a/documentos/transversales/05_Presupuesto_SIGEVET.xlsx
+++ b/documentos/transversales/05_Presupuesto_SIGEVET.xlsx
@@ -955,7 +955,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Java/Tomcat</t>
+          <t>Java/Spring Boot</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
